--- a/data/Excel/GuLiStrikeSecondaryUnitSkills.xlsx
+++ b/data/Excel/GuLiStrikeSecondaryUnitSkills.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>id</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>战争机器Q；每台独立6秒；射程取最终普通攻击x1.6（基线48米）；直径8米圆内独立随机落点，圆心验射程、落点允许越界；爆炸与预警半径1.6米，伤害与挂点引用武器槽</t>
+  </si>
+  <si>
+    <t>战争机器Q；每台独立6秒；射程取最终普通攻击x1.6（基线48米）；直径16米圆内独立随机落点，圆心验射程、落点允许越界；爆炸与预警半径2米，伤害与挂点引用武器槽</t>
   </si>
 </sst>
 </file>
@@ -664,7 +667,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -709,7 +712,7 @@
         <v>45</v>
       </c>
       <c r="R4">
-        <v>800</v>
+        <v>1600</v>
       </c>
     </row>
   </sheetData>

--- a/data/Excel/GuLiStrikeSecondaryUnitSkills.xlsx
+++ b/data/Excel/GuLiStrikeSecondaryUnitSkills.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>id</t>
   </si>
@@ -168,6 +168,15 @@
   </si>
   <si>
     <t>战争机器Q；每台独立6秒；射程取最终普通攻击x1.6（基线48米）；直径16米圆内独立随机落点，圆心验射程、落点允许越界；爆炸与预警半径2米，伤害与挂点引用武器槽</t>
+  </si>
+  <si>
+    <t>重防号Q；每台独立6秒；射程取最终普通攻击x1.6（基线48米）；直径16米圆内独立随机落点，圆心验射程、落点允许越界；爆炸与预警半径2米，伤害与挂点引用武器槽</t>
+  </si>
+  <si>
+    <t>重防号；空技能表示当前无主动Q</t>
+  </si>
+  <si>
+    <t>重防号Q；每台独立6秒；射程取最终普通攻击x3.2（基线96米）；直径16米圆内独立随机落点，圆心验射程、落点允许越界；爆炸与预警半径3米，伤害与挂点引用武器槽</t>
   </si>
 </sst>
 </file>
@@ -667,7 +676,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -676,13 +685,13 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <v>4800</v>
+        <v>9600</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
       </c>
       <c r="H4">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -801,7 +810,7 @@
         <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D5">
         <v>2</v>

--- a/data/Excel/GuLiStrikeSecondaryUnitSkills.xlsx
+++ b/data/Excel/GuLiStrikeSecondaryUnitSkills.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>id</t>
   </si>
@@ -177,6 +177,57 @@
   </si>
   <si>
     <t>重防号Q；每台独立6秒；射程取最终普通攻击x3.2（基线96米）；直径16米圆内独立随机落点，圆心验射程、落点允许越界；爆炸与预警半径3米，伤害与挂点引用武器槽</t>
+  </si>
+  <si>
+    <t>MaxProjectilesPerActivation</t>
+  </si>
+  <si>
+    <t>重防号Q；每圈最多60发，整台齐射不拆分，未分配单位留待下一Q；成功单位独立6秒冷却；共享引导圈半径8米，保留单弹3米预警；射程取最终普攻x3.2，落点在直径16米内随机。</t>
+  </si>
+  <si>
+    <t>重防号Q；每圈最多60发，整台齐射不拆分，未分配单位留待下一Q；成功单位独立6秒冷却；共享引导圈半径8米，保留单弹3米预警；射程取最终普攻x2，基础240米（2026-10-01由96米x2.5），落点在直径16米内随机。</t>
+  </si>
+  <si>
+    <t>SummonUnitTypeId</t>
+  </si>
+  <si>
+    <t>SummonCount</t>
+  </si>
+  <si>
+    <t>SummonClearanceCentimeters</t>
+  </si>
+  <si>
+    <t>SummonOuterRings</t>
+  </si>
+  <si>
+    <t>SummonCandidatesPerRing</t>
+  </si>
+  <si>
+    <t>Pioneer_Summon</t>
+  </si>
+  <si>
+    <t>Q立即召唤五个扫荡者；每台独立30秒；整批5或0；免费且不计人口</t>
+  </si>
+  <si>
+    <t>Self</t>
+  </si>
+  <si>
+    <t>/Script/GuLiStrike.GuLiSummonSkillExecutor</t>
+  </si>
+  <si>
+    <t>/Script/GuLiStrike.GuLiSummonSkillConfiguration</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Commander/Skills/DA_Pioneer_Summon</t>
+  </si>
+  <si>
+    <t>先驱号默认解锁Q召唤</t>
+  </si>
+  <si>
+    <t>SweeperSummon</t>
+  </si>
+  <si>
+    <t>召唤扫荡者无主动Q</t>
   </si>
 </sst>
 </file>
@@ -555,6 +606,24 @@
       <c r="R1" t="s">
         <v>47</v>
       </c>
+      <c r="S1" t="s">
+        <v>54</v>
+      </c>
+      <c r="T1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U1" t="s">
+        <v>58</v>
+      </c>
+      <c r="V1" t="s">
+        <v>59</v>
+      </c>
+      <c r="W1" t="s">
+        <v>60</v>
+      </c>
+      <c r="X1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
@@ -611,6 +680,24 @@
       <c r="R2" t="s">
         <v>12</v>
       </c>
+      <c r="S2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" t="s">
+        <v>12</v>
+      </c>
+      <c r="W2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -667,6 +754,24 @@
       <c r="R3" t="s">
         <v>7</v>
       </c>
+      <c r="S3" t="s">
+        <v>7</v>
+      </c>
+      <c r="T3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U3" t="s">
+        <v>7</v>
+      </c>
+      <c r="V3" t="s">
+        <v>7</v>
+      </c>
+      <c r="W3" t="s">
+        <v>7</v>
+      </c>
+      <c r="X3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -676,7 +781,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -685,13 +790,13 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <v>9600</v>
+        <v>24000</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
       </c>
       <c r="H4">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -722,6 +827,59 @@
       </c>
       <c r="R4">
         <v>1600</v>
+      </c>
+      <c r="S4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5">
+        <v>30</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L5" t="s">
+        <v>67</v>
+      </c>
+      <c r="T5">
+        <v>5</v>
+      </c>
+      <c r="U5">
+        <v>5</v>
+      </c>
+      <c r="V5">
+        <v>50</v>
+      </c>
+      <c r="W5">
+        <v>3</v>
+      </c>
+      <c r="X5">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -796,10 +954,13 @@
         <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="D4">
         <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -847,6 +1008,20 @@
         <v>4</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>